--- a/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
+++ b/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -301,16 +301,266 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Sarah Gottlieb' Employee:{10699038}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//div[@data-automation-id="tooltipsWrapper"]/button[@data-automation-id="inbox_preview"]').first()[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #60[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
   </si>
   <si>
     <t>Hungary</t>
   </si>
   <si>
-    <t>Wilmer</t>
-  </si>
-  <si>
-    <t>Lebsack</t>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Gottlieb</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -467,13 +717,13 @@
     <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
   <si>
-    <t>Gayle</t>
-  </si>
-  <si>
-    <t>Wuckert</t>
-  </si>
-  <si>
-    <t>Auto 15654745</t>
+    <t>Lela</t>
+  </si>
+  <si>
+    <t>Kuhic</t>
+  </si>
+  <si>
+    <t>Auto 60703751</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -1334,89 +1584,94 @@
       <c r="A2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K2" s="8">
         <f t="shared" ref="K2:K3" si="0">TODAY()-31</f>
         <v>45755</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N2" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="O2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="V2" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y2" s="8">
         <f t="shared" ref="Y2:Y3" si="1">K2</f>
         <v>45755</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AA2" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AB2" s="17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AC2" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AD2" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AE2" s="9">
         <v>846</v>
@@ -1428,10 +1683,10 @@
         <v>40</v>
       </c>
       <c r="AH2" s="18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AI2" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AJ2" s="20">
         <f>TODAY()+365</f>
@@ -1442,38 +1697,38 @@
         <v>45845</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AM2" s="18" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AN2" s="22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AP2" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AR2" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AS2" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AT2" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AU2" s="17" t="str">
         <f t="shared" ref="AU2:AU3" si="3">AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AW2" s="23">
         <f t="shared" ref="AW2:AW3" si="4">Y2-1</f>
@@ -1488,30 +1743,30 @@
         <v>46151</v>
       </c>
       <c r="AZ2" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA2" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BB2" s="25">
         <f t="array" ref="BB2:BB3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>252039795</v>
+        <v>123516165</v>
       </c>
       <c r="BC2" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BD2" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BE2" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BG2" s="25">
         <f t="array" ref="BG2:BG3">_xlfn.RANDARRAY(2,1,1234567890,9999999999,TRUE)</f>
-        <v>2224932913</v>
+        <v>7299708540</v>
       </c>
       <c r="BH2" s="14">
         <v>36526</v>
@@ -1520,162 +1775,162 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK2" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BL2" s="26">
         <v>32875</v>
       </c>
       <c r="BM2" s="27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BO2" s="22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP2" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BQ2" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BR2" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS2" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BT2" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BU2" s="22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BV2" s="22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BW2" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BX2" s="29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BY2" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="BZ2" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="CA2" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="CB2" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="CC2" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="BZ2" s="13" t="s">
+      <c r="CD2" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="CA2" s="30" t="s">
+      <c r="CE2" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="CB2" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="CC2" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="CD2" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="CE2" s="30" t="s">
-        <v>138</v>
-      </c>
       <c r="CF2" s="30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CG2" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CH2" s="30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CI2" s="30">
         <v>100</v>
       </c>
       <c r="CJ2" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="CK2" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="CL2" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM2" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="CN2" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CO2" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CP2" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CQ2" s="31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CR2" s="32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CS2" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CU2" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CV2" s="30"/>
     </row>
     <row r="3" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K3" s="8">
         <f t="shared" si="0"/>
         <v>45755</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P3" s="12">
         <v>3</v>
@@ -1687,41 +1942,41 @@
         <v>1046</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V3" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" si="1"/>
         <v>45755</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AA3" s="16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AB3" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AD3" s="19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AE3" s="9">
         <v>846</v>
@@ -1733,51 +1988,51 @@
         <v>10</v>
       </c>
       <c r="AH3" s="18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AI3" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AJ3" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK3" s="21">
         <f t="shared" si="2"/>
         <v>45845</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AM3" s="18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AN3" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AP3" s="18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AQ3" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AR3" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AS3" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AT3" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AU3" s="17" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AW3" s="23">
         <f t="shared" si="4"/>
@@ -1792,13 +2047,13 @@
         <v>N/A</v>
       </c>
       <c r="AZ3" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BB3" s="25">
-        <v>402930100</v>
+        <v>888596532</v>
       </c>
       <c r="BC3" s="14">
         <v>36526</v>
@@ -1807,13 +2062,13 @@
         <v>51136</v>
       </c>
       <c r="BE3" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BG3" s="25">
-        <v>5938913381</v>
+        <v>1446449727</v>
       </c>
       <c r="BH3" s="14">
         <v>36526</v>
@@ -1822,112 +2077,112 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK3" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BL3" s="26">
         <v>32875</v>
       </c>
       <c r="BM3" s="27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BO3" s="22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP3" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BQ3" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BR3" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BS3" s="18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BT3" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BU3" s="22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BV3" s="22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BW3" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BX3" s="29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BY3" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BZ3" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="CA3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CB3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CC3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CD3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CE3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CF3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CG3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CH3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CI3" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="CJ3" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="CK3" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="CL3" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CM3" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="CN3" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CO3" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="CP3" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="CQ3" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="CR3" s="32">
         <v>31048</v>
       </c>
       <c r="CS3" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CT3" s="30">
         <v>1234011</v>

--- a/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
+++ b/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6800588-3561-4AE5-BC83-CF8691601FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="166">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -301,256 +315,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Sarah Gottlieb' Employee:{10699038}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//div[@data-automation-id="tooltipsWrapper"]/button[@data-automation-id="inbox_preview"]').first()[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #59[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not visible[22m
-[2m  - retrying click action, attempt #60[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>846 Recruitment (Sekive Solav (10632957))</t>
   </si>
   <si>
@@ -623,7 +387,7 @@
     <t>Automation Comments here….</t>
   </si>
   <si>
-    <t xml:space="preserve">94 Retail Operatives </t>
+    <t>94 Retail Operatives </t>
   </si>
   <si>
     <t>16 Men’s Accessories</t>
@@ -738,7 +502,7 @@
     <t>IRREGULAR - Irregular Shift Pattern (Hungary Regular &amp; Irregular Shift Pattern-Hungary)</t>
   </si>
   <si>
-    <t xml:space="preserve">92 Retail Management </t>
+    <t>92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -768,50 +532,50 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -834,7 +598,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,24 +612,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1232,9 +1016,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CV3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="18.81640625" customWidth="1"/>
@@ -1258,6 +1042,7 @@
     <col min="46" max="46" width="23.1796875" customWidth="1"/>
     <col min="49" max="49" width="24.26953125" customWidth="1"/>
     <col min="50" max="50" width="33.6328125" customWidth="1"/>
+    <col min="51" max="51" width="14.453125" customWidth="1"/>
     <col min="52" max="52" width="38.453125" customWidth="1"/>
     <col min="53" max="53" width="34.08984375" customWidth="1"/>
     <col min="54" max="54" width="43.26953125" customWidth="1"/>
@@ -1270,6 +1055,8 @@
     <col min="64" max="64" width="29.453125" customWidth="1"/>
     <col min="65" max="65" width="34.36328125" customWidth="1"/>
     <col min="66" max="66" width="26.08984375" customWidth="1"/>
+    <col min="71" max="71" width="13.08984375" customWidth="1"/>
+    <col min="72" max="72" width="13.36328125" customWidth="1"/>
     <col min="78" max="78" width="21.6328125" customWidth="1"/>
     <col min="79" max="79" width="23.26953125" customWidth="1"/>
     <col min="89" max="89" width="29.36328125" customWidth="1"/>
@@ -1281,7 +1068,7 @@
     <col min="99" max="99" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:99" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:100" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,98 +1367,93 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="8">
+        <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K2" s="8">
-        <f t="shared" ref="K2:K3" si="0">TODAY()-31</f>
-        <v>45755</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="O2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="P2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="Q2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="R2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="T2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="V2" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="W2" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="V2" s="14" t="s">
+      <c r="X2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y2" s="8">
+        <f t="shared" ref="Y2:Y3" ca="1" si="1">K2</f>
+        <v>45761</v>
+      </c>
+      <c r="Z2" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="W2" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y2" s="8">
-        <f t="shared" ref="Y2:Y3" si="1">K2</f>
-        <v>45755</v>
-      </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AA2" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB2" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AC2" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="17" t="s">
+      <c r="AD2" s="19" t="s">
         <v>115</v>
-      </c>
-      <c r="AC2" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD2" s="19" t="s">
-        <v>117</v>
       </c>
       <c r="AE2" s="9">
         <v>846</v>
@@ -1683,90 +1465,90 @@
         <v>40</v>
       </c>
       <c r="AH2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AJ2" s="20">
+        <f ca="1">TODAY()+365</f>
+        <v>46157</v>
+      </c>
+      <c r="AK2" s="21">
+        <f t="shared" ref="AK2:AK3" ca="1" si="2">Y2+90</f>
+        <v>45851</v>
+      </c>
+      <c r="AL2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="AI2" s="9" t="s">
+      <c r="AM2" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="AJ2" s="20">
-        <f>TODAY()+365</f>
-        <v>46151</v>
-      </c>
-      <c r="AK2" s="21">
-        <f t="shared" ref="AK2:AK3" si="2">Y2+90</f>
-        <v>45845</v>
-      </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AN2" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AO2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AP2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AP2" s="18" t="s">
+      <c r="AR2" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT2" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="AQ2" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AR2" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS2" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AT2" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="AU2" s="17" t="str">
         <f t="shared" ref="AU2:AU3" si="3">AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="AW2" s="23">
+        <f t="shared" ref="AW2:AW3" ca="1" si="4">Y2-1</f>
+        <v>45760</v>
+      </c>
+      <c r="AX2" s="23">
+        <f t="shared" ref="AX2:AX3" ca="1" si="5">Y2-1</f>
+        <v>45760</v>
+      </c>
+      <c r="AY2" s="23">
+        <f t="shared" ref="AY2:AY3" ca="1" si="6">AJ2</f>
+        <v>46157</v>
+      </c>
+      <c r="AZ2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="BA2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB2" s="25">
+        <f t="array" aca="1" ref="BB2:BB3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>453042829</v>
+      </c>
+      <c r="BC2" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AW2" s="23">
-        <f t="shared" ref="AW2:AW3" si="4">Y2-1</f>
-        <v>45754</v>
-      </c>
-      <c r="AX2" s="23">
-        <f t="shared" ref="AX2:AX3" si="5">Y2-1</f>
-        <v>45754</v>
-      </c>
-      <c r="AY2" s="24">
-        <f t="shared" ref="AY2:AY3" si="6">AJ2</f>
-        <v>46151</v>
-      </c>
-      <c r="AZ2" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA2" s="13" t="s">
+      <c r="BD2" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="BB2" s="25">
-        <f t="array" ref="BB2:BB3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>123516165</v>
-      </c>
-      <c r="BC2" s="14" t="s">
+      <c r="BE2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="BF2" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="BD2" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE2" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="BF2" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="BG2" s="25">
-        <f t="array" ref="BG2:BG3">_xlfn.RANDARRAY(2,1,1234567890,9999999999,TRUE)</f>
-        <v>7299708540</v>
+        <f t="array" aca="1" ref="BG2:BG3" ca="1">_xlfn.RANDARRAY(2,1,1234567890,9999999999,TRUE)</f>
+        <v>5519905884</v>
       </c>
       <c r="BH2" s="14">
         <v>36526</v>
@@ -1775,162 +1557,162 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="BK2" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BL2" s="26">
         <v>32875</v>
       </c>
       <c r="BM2" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BO2" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP2" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="BQ2" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BR2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="BS2" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT2" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU2" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="BP2" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ2" s="13" t="s">
+      <c r="BV2" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="BR2" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="BS2" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="BT2" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BU2" s="22" t="s">
+      <c r="BW2" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BV2" s="22" t="s">
+      <c r="BX2" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="BW2" s="13" t="s">
+      <c r="BY2" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BX2" s="29" t="s">
+      <c r="BZ2" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="BY2" s="13" t="s">
+      <c r="CA2" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="BZ2" s="13" t="s">
+      <c r="CB2" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="CA2" s="30" t="s">
+      <c r="CC2" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="CD2" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="CE2" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="CF2" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="CB2" s="30" t="s">
+      <c r="CG2" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="CC2" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="CD2" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="CE2" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="CF2" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="CG2" s="30" t="s">
-        <v>145</v>
-      </c>
       <c r="CH2" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="CI2" s="30">
         <v>100</v>
       </c>
       <c r="CJ2" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="CK2" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="CL2" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="CM2" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="CK2" s="13" t="s">
+      <c r="CN2" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="CL2" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="CM2" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="CN2" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="CO2" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CP2" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CQ2" s="31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CR2" s="32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CS2" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CT2" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CU2" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="CV2" s="30"/>
     </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="H3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="K3" s="8">
+        <f t="shared" ca="1" si="0"/>
+        <v>45761</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="K3" s="8">
-        <f t="shared" si="0"/>
-        <v>45755</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P3" s="12">
         <v>3</v>
@@ -1942,41 +1724,41 @@
         <v>1046</v>
       </c>
       <c r="S3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="V3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="T3" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="V3" s="14" t="s">
+      <c r="X3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y3" s="8">
+        <f t="shared" ca="1" si="1"/>
+        <v>45761</v>
+      </c>
+      <c r="Z3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="W3" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y3" s="8">
-        <f t="shared" si="1"/>
-        <v>45755</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="AA3" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC3" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="AB3" s="17" t="s">
+      <c r="AD3" s="19" t="s">
         <v>155</v>
-      </c>
-      <c r="AC3" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="AD3" s="19" t="s">
-        <v>157</v>
       </c>
       <c r="AE3" s="9">
         <v>846</v>
@@ -1988,72 +1770,73 @@
         <v>10</v>
       </c>
       <c r="AH3" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AJ3" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK3" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>45851</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM3" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="AN3" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="AI3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="AJ3" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK3" s="21">
-        <f t="shared" si="2"/>
-        <v>45845</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM3" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="AN3" s="22" t="s">
-        <v>160</v>
-      </c>
       <c r="AO3" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AP3" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AP3" s="18" t="s">
+      <c r="AR3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT3" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AR3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="AS3" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AT3" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="AU3" s="17" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AW3" s="23">
-        <f t="shared" si="4"/>
-        <v>45754</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45760</v>
       </c>
       <c r="AX3" s="23">
-        <f t="shared" si="5"/>
-        <v>45754</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>45760</v>
       </c>
       <c r="AY3" s="24" t="str">
         <f t="shared" si="6"/>
         <v>N/A</v>
       </c>
       <c r="AZ3" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BB3" s="25">
-        <v>888596532</v>
+        <f ca="1"/>
+        <v>439008994</v>
       </c>
       <c r="BC3" s="14">
         <v>36526</v>
@@ -2062,13 +1845,14 @@
         <v>51136</v>
       </c>
       <c r="BE3" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="BG3" s="25">
-        <v>1446449727</v>
+        <f ca="1"/>
+        <v>2311547315</v>
       </c>
       <c r="BH3" s="14">
         <v>36526</v>
@@ -2077,112 +1861,112 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="BK3" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BL3" s="26">
         <v>32875</v>
       </c>
       <c r="BM3" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BO3" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP3" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="BQ3" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="BS3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT3" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU3" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="BP3" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="BQ3" s="13" t="s">
+      <c r="BV3" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="BR3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="BS3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="BT3" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BU3" s="22" t="s">
+      <c r="BW3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BV3" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BW3" s="13" t="s">
+      <c r="BX3" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="BY3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BX3" s="29" t="s">
+      <c r="BZ3" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="CA3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CD3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CF3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CG3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CH3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CI3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CJ3" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="CK3" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="CL3" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="CM3" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="CN3" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="CO3" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="BY3" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="BZ3" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="CA3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CB3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CC3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CD3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CE3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CF3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CG3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CH3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CI3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="CJ3" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="CK3" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="CL3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="CM3" s="13" t="s">
+      <c r="CP3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="CN3" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="CO3" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="CP3" s="19" t="s">
-        <v>166</v>
-      </c>
       <c r="CQ3" s="31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="CR3" s="32">
         <v>31048</v>
       </c>
       <c r="CS3" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="CT3" s="30">
         <v>1234011</v>
@@ -2193,52 +1977,19 @@
       <c r="CV3" s="30"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 Z2 X2 U2 I2:J2 CC2 BW2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:J3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3">
-      <formula1>INDIRECT($E3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
-      <formula1>INDIRECT($C2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV3 Z3 X3 U3 I3:J3 BW3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="W2" r:id="rId1"/>
-    <hyperlink ref="W3" r:id="rId2"/>
+    <hyperlink ref="W2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="W3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
+++ b/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6800588-3561-4AE5-BC83-CF8691601FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D0A12-1995-41A0-8EFD-741D57B4BCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="166">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -321,10 +321,10 @@
     <t>Hungary</t>
   </si>
   <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Gottlieb</t>
+    <t>Agustin</t>
+  </si>
+  <si>
+    <t>Emmerich</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -713,7 +713,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -737,6 +736,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1530,9 +1530,9 @@
       <c r="BA2" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="BB2" s="25">
+      <c r="BB2" s="24">
         <f t="array" aca="1" ref="BB2:BB3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>453042829</v>
+        <v>806872257</v>
       </c>
       <c r="BC2" s="14" t="s">
         <v>127</v>
@@ -1546,9 +1546,9 @@
       <c r="BF2" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="BG2" s="25">
+      <c r="BG2" s="24">
         <f t="array" aca="1" ref="BG2:BG3" ca="1">_xlfn.RANDARRAY(2,1,1234567890,9999999999,TRUE)</f>
-        <v>5519905884</v>
+        <v>2155110841</v>
       </c>
       <c r="BH2" s="14">
         <v>36526</v>
@@ -1562,10 +1562,10 @@
       <c r="BK2" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="BL2" s="26">
+      <c r="BL2" s="25">
         <v>32875</v>
       </c>
-      <c r="BM2" s="27" t="s">
+      <c r="BM2" s="26" t="s">
         <v>96</v>
       </c>
       <c r="BN2" s="13" t="s">
@@ -1574,7 +1574,7 @@
       <c r="BO2" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="BP2" s="28" t="s">
+      <c r="BP2" s="27" t="s">
         <v>112</v>
       </c>
       <c r="BQ2" s="13" t="s">
@@ -1584,10 +1584,10 @@
         <v>96</v>
       </c>
       <c r="BS2" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="BT2" s="19" t="s">
-        <v>112</v>
+        <v>122</v>
+      </c>
+      <c r="BT2" s="19">
+        <v>10</v>
       </c>
       <c r="BU2" s="22" t="s">
         <v>134</v>
@@ -1598,7 +1598,7 @@
       <c r="BW2" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BX2" s="29" t="s">
+      <c r="BX2" s="28" t="s">
         <v>137</v>
       </c>
       <c r="BY2" s="13" t="s">
@@ -1607,31 +1607,31 @@
       <c r="BZ2" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="CA2" s="30" t="s">
+      <c r="CA2" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="CB2" s="30" t="s">
+      <c r="CB2" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="CC2" s="30" t="s">
+      <c r="CC2" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="CD2" s="30" t="s">
+      <c r="CD2" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="CE2" s="30" t="s">
+      <c r="CE2" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="CF2" s="30" t="s">
+      <c r="CF2" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="CG2" s="30" t="s">
+      <c r="CG2" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="CH2" s="30" t="s">
+      <c r="CH2" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="CI2" s="30">
+      <c r="CI2" s="29">
         <v>100</v>
       </c>
       <c r="CJ2" s="13" t="s">
@@ -1655,22 +1655,22 @@
       <c r="CP2" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="CQ2" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="CR2" s="32" t="s">
+      <c r="CQ2" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="CR2" s="31" t="s">
         <v>112</v>
       </c>
       <c r="CS2" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="CT2" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CU2" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CV2" s="30"/>
+      <c r="CT2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CU2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CV2" s="29"/>
     </row>
     <row r="3" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -1824,7 +1824,7 @@
         <f t="shared" ca="1" si="5"/>
         <v>45760</v>
       </c>
-      <c r="AY3" s="24" t="str">
+      <c r="AY3" s="32" t="str">
         <f t="shared" si="6"/>
         <v>N/A</v>
       </c>
@@ -1834,9 +1834,9 @@
       <c r="BA3" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="BB3" s="25">
+      <c r="BB3" s="24">
         <f ca="1"/>
-        <v>439008994</v>
+        <v>565547653</v>
       </c>
       <c r="BC3" s="14">
         <v>36526</v>
@@ -1850,9 +1850,9 @@
       <c r="BF3" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="BG3" s="25">
+      <c r="BG3" s="24">
         <f ca="1"/>
-        <v>2311547315</v>
+        <v>1708958577</v>
       </c>
       <c r="BH3" s="14">
         <v>36526</v>
@@ -1866,10 +1866,10 @@
       <c r="BK3" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="BL3" s="26">
+      <c r="BL3" s="25">
         <v>32875</v>
       </c>
-      <c r="BM3" s="27" t="s">
+      <c r="BM3" s="26" t="s">
         <v>96</v>
       </c>
       <c r="BN3" s="13" t="s">
@@ -1878,7 +1878,7 @@
       <c r="BO3" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="BP3" s="28" t="s">
+      <c r="BP3" s="27" t="s">
         <v>112</v>
       </c>
       <c r="BQ3" s="13" t="s">
@@ -1902,7 +1902,7 @@
       <c r="BW3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BX3" s="29" t="s">
+      <c r="BX3" s="28" t="s">
         <v>161</v>
       </c>
       <c r="BY3" s="13" t="s">
@@ -1911,31 +1911,31 @@
       <c r="BZ3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="CA3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CB3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CC3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CD3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CE3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CF3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CG3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CH3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CI3" s="30" t="s">
+      <c r="CA3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CB3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CC3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CD3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CE3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CF3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CG3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CH3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="CI3" s="29" t="s">
         <v>112</v>
       </c>
       <c r="CJ3" s="13" t="s">
@@ -1959,22 +1959,22 @@
       <c r="CP3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="CQ3" s="31" t="s">
+      <c r="CQ3" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="CR3" s="32">
+      <c r="CR3" s="31">
         <v>31048</v>
       </c>
       <c r="CS3" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="CT3" s="30">
+      <c r="CT3" s="29">
         <v>1234011</v>
       </c>
-      <c r="CU3" s="30">
+      <c r="CU3" s="29">
         <v>123456011</v>
       </c>
-      <c r="CV3" s="30"/>
+      <c r="CV3" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
+++ b/Data/Workday_NewHire_Hungary_Regression_PK17.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D0A12-1995-41A0-8EFD-741D57B4BCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EEF0A4-2A7C-49F3-814B-5E7EF87B5298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="162">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -319,12 +319,6 @@
   </si>
   <si>
     <t>Hungary</t>
-  </si>
-  <si>
-    <t>Agustin</t>
-  </si>
-  <si>
-    <t>Emmerich</t>
   </si>
   <si>
     <t>(061)2123123</t>
@@ -481,13 +475,7 @@
     <t>846 Store Management (Zavamy Pyfaw (10632958))</t>
   </si>
   <si>
-    <t>Lela</t>
-  </si>
-  <si>
-    <t>Kuhic</t>
-  </si>
-  <si>
-    <t>Auto 60703751</t>
+    <t>Auto 37194876</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -705,9 +693,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -734,6 +719,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1378,82 +1366,78 @@
       <c r="E2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="K2" s="8">
         <f t="shared" ref="K2:K3" ca="1" si="0">TODAY()-31</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="L2" s="9" t="s">
         <v>96</v>
       </c>
       <c r="M2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="P2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="Q2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="R2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="T2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="W2" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>110</v>
-      </c>
       <c r="X2" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Y2" s="8">
         <f t="shared" ref="Y2:Y3" ca="1" si="1">K2</f>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="Z2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA2" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AC2" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="AB2" s="17" t="s">
+      <c r="AD2" s="19" t="s">
         <v>113</v>
-      </c>
-      <c r="AC2" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD2" s="19" t="s">
-        <v>115</v>
       </c>
       <c r="AE2" s="9">
         <v>846</v>
@@ -1465,90 +1449,90 @@
         <v>40</v>
       </c>
       <c r="AH2" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AI2" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AJ2" s="20">
         <f ca="1">TODAY()+365</f>
-        <v>46157</v>
-      </c>
-      <c r="AK2" s="21">
+        <v>46158</v>
+      </c>
+      <c r="AK2" s="20">
         <f t="shared" ref="AK2:AK3" ca="1" si="2">Y2+90</f>
-        <v>45851</v>
+        <v>45852</v>
       </c>
       <c r="AL2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN2" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AO2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AP2" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="AP2" s="18" t="s">
+      <c r="AR2" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT2" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="AQ2" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR2" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="AS2" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT2" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="AU2" s="17" t="str">
         <f t="shared" ref="AU2:AU3" si="3">AB2</f>
         <v>Fixed Term (Fixed Term)</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW2" s="23">
+        <v>123</v>
+      </c>
+      <c r="AW2" s="22">
         <f t="shared" ref="AW2:AW3" ca="1" si="4">Y2-1</f>
-        <v>45760</v>
-      </c>
-      <c r="AX2" s="23">
+        <v>45761</v>
+      </c>
+      <c r="AX2" s="22">
         <f t="shared" ref="AX2:AX3" ca="1" si="5">Y2-1</f>
-        <v>45760</v>
-      </c>
-      <c r="AY2" s="23">
+        <v>45761</v>
+      </c>
+      <c r="AY2" s="22">
         <f t="shared" ref="AY2:AY3" ca="1" si="6">AJ2</f>
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="AZ2" s="13" t="s">
         <v>96</v>
       </c>
       <c r="BA2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB2" s="23">
+        <f t="array" aca="1" ref="BB2:BB3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>697283307</v>
+      </c>
+      <c r="BC2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD2" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="BB2" s="24">
-        <f t="array" aca="1" ref="BB2:BB3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>806872257</v>
-      </c>
-      <c r="BC2" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="BD2" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="BE2" s="13" t="s">
         <v>96</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BG2" s="24">
+        <v>127</v>
+      </c>
+      <c r="BG2" s="23">
         <f t="array" aca="1" ref="BG2:BG3" ca="1">_xlfn.RANDARRAY(2,1,1234567890,9999999999,TRUE)</f>
-        <v>2155110841</v>
+        <v>4097787791</v>
       </c>
       <c r="BH2" s="14">
         <v>36526</v>
@@ -1557,208 +1541,204 @@
         <v>51136</v>
       </c>
       <c r="BJ2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK2" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="BL2" s="24">
+        <v>32875</v>
+      </c>
+      <c r="BM2" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="BO2" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="BK2" s="18" t="s">
+      <c r="BP2" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="BQ2" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="BL2" s="25">
-        <v>32875</v>
-      </c>
-      <c r="BM2" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO2" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP2" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="BQ2" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="BR2" s="13" t="s">
         <v>96</v>
       </c>
       <c r="BS2" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BT2" s="19">
         <v>10</v>
       </c>
-      <c r="BU2" s="22" t="s">
+      <c r="BU2" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="BV2" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="BW2" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="BV2" s="22" t="s">
+      <c r="BX2" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="BW2" s="13" t="s">
+      <c r="BY2" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BX2" s="28" t="s">
+      <c r="BZ2" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="BY2" s="13" t="s">
+      <c r="CA2" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="BZ2" s="13" t="s">
+      <c r="CB2" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="CA2" s="29" t="s">
+      <c r="CC2" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD2" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="CE2" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="CF2" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="CB2" s="29" t="s">
+      <c r="CG2" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="CC2" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="CD2" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="CE2" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="CF2" s="29" t="s">
+      <c r="CH2" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="CI2" s="28">
+        <v>100</v>
+      </c>
+      <c r="CJ2" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="CG2" s="29" t="s">
+      <c r="CK2" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="CH2" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="CI2" s="29">
-        <v>100</v>
-      </c>
-      <c r="CJ2" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="CK2" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="CL2" s="13" t="s">
         <v>96</v>
       </c>
       <c r="CM2" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="CN2" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="CO2" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="CP2" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="CQ2" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="CR2" s="31" t="s">
-        <v>112</v>
+        <v>110</v>
+      </c>
+      <c r="CQ2" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="CR2" s="30" t="s">
+        <v>110</v>
       </c>
       <c r="CS2" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="CT2" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CU2" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CV2" s="29"/>
+        <v>110</v>
+      </c>
+      <c r="CT2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CU2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CV2" s="28"/>
     </row>
     <row r="3" spans="1:100" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="K3" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>96</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N3" s="7">
         <v>1</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P3" s="12">
         <v>3</v>
       </c>
-      <c r="Q3" s="7">
-        <v>123</v>
-      </c>
-      <c r="R3" s="7">
-        <v>1046</v>
+      <c r="Q3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="S3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="V3" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="T3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="V3" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>110</v>
-      </c>
       <c r="X3" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" ca="1" si="1"/>
-        <v>45761</v>
+        <v>45762</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA3" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="AB3" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AD3" s="19" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AE3" s="9">
         <v>846</v>
@@ -1770,59 +1750,59 @@
         <v>10</v>
       </c>
       <c r="AH3" s="18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AI3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ3" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="AK3" s="21">
+        <v>115</v>
+      </c>
+      <c r="AJ3" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK3" s="20">
         <f t="shared" ca="1" si="2"/>
-        <v>45851</v>
+        <v>45852</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AM3" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="AN3" s="22" t="s">
-        <v>158</v>
+        <v>153</v>
+      </c>
+      <c r="AN3" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="AO3" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP3" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="AP3" s="18" t="s">
+      <c r="AR3" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT3" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AR3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="AS3" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT3" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="AU3" s="17" t="str">
         <f t="shared" si="3"/>
         <v>Permanent</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW3" s="23">
+        <v>123</v>
+      </c>
+      <c r="AW3" s="22">
         <f t="shared" ca="1" si="4"/>
-        <v>45760</v>
-      </c>
-      <c r="AX3" s="23">
+        <v>45761</v>
+      </c>
+      <c r="AX3" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>45760</v>
+        <v>45761</v>
       </c>
       <c r="AY3" s="32" t="str">
         <f t="shared" si="6"/>
@@ -1832,11 +1812,11 @@
         <v>96</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="BB3" s="24">
+        <v>155</v>
+      </c>
+      <c r="BB3" s="23">
         <f ca="1"/>
-        <v>565547653</v>
+        <v>747070771</v>
       </c>
       <c r="BC3" s="14">
         <v>36526</v>
@@ -1848,11 +1828,11 @@
         <v>96</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BG3" s="24">
+        <v>127</v>
+      </c>
+      <c r="BG3" s="23">
         <f ca="1"/>
-        <v>1708958577</v>
+        <v>7172281713</v>
       </c>
       <c r="BH3" s="14">
         <v>36526</v>
@@ -1861,120 +1841,120 @@
         <v>51136</v>
       </c>
       <c r="BJ3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BK3" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="BL3" s="24">
+        <v>32875</v>
+      </c>
+      <c r="BM3" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="BO3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="BK3" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="BL3" s="25">
-        <v>32875</v>
-      </c>
-      <c r="BM3" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO3" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP3" s="27" t="s">
-        <v>112</v>
+      <c r="BP3" s="26" t="s">
+        <v>110</v>
       </c>
       <c r="BQ3" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BR3" s="13" t="s">
         <v>96</v>
       </c>
       <c r="BS3" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="BT3" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="BU3" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="BU3" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="BV3" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="BW3" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="BV3" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="BW3" s="13" t="s">
+      <c r="BX3" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="BY3" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="BX3" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="BY3" s="13" t="s">
-        <v>138</v>
-      </c>
       <c r="BZ3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="CA3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CB3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CC3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CD3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CE3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CF3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CG3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CH3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="CI3" s="29" t="s">
-        <v>112</v>
+        <v>137</v>
+      </c>
+      <c r="CA3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CB3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CC3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CD3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CE3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CF3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CG3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CH3" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="CI3" s="28" t="s">
+        <v>110</v>
       </c>
       <c r="CJ3" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="CK3" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="CL3" s="13" t="s">
         <v>96</v>
       </c>
       <c r="CM3" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="CN3" s="13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="CO3" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="CP3" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="CQ3" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="CR3" s="31">
+        <v>160</v>
+      </c>
+      <c r="CQ3" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="CR3" s="30">
         <v>31048</v>
       </c>
       <c r="CS3" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="CT3" s="29">
+        <v>161</v>
+      </c>
+      <c r="CT3" s="28">
         <v>1234011</v>
       </c>
-      <c r="CU3" s="29">
+      <c r="CU3" s="28">
         <v>123456011</v>
       </c>
-      <c r="CV3" s="29"/>
+      <c r="CV3" s="28"/>
     </row>
   </sheetData>
   <dataValidations count="2">
